--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1656,7 +1656,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>584105-220-CM26</t>
+          <t>1480972-683-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1681,32 +1681,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>558.01</v>
+        <v>24797.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1480972-683-CM26</t>
+          <t>1978-1091-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1746,32 +1746,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24797.16</v>
+        <v>49106.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3992-187-CM26</t>
+          <t>5418-237-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1811,27 +1811,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>35720.72</v>
+        <v>17238.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>640840-181-CM26</t>
+          <t>3992-187-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1876,32 +1876,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>433.64</v>
+        <v>35720.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1978-1091-CM26</t>
+          <t>640840-181-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1941,32 +1941,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>49106.06</v>
+        <v>433.64</v>
       </c>
     </row>
     <row r="25">
@@ -2107,7 +2107,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5418-237-CM26</t>
+          <t>584105-220-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>17238.34</v>
+        <v>558.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2859-1180-CM26</t>
+          <t>2852-1059-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2197,27 +2197,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5760.27</v>
+        <v>34955.73</v>
       </c>
     </row>
     <row r="29">
@@ -2432,7 +2432,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2852-1059-CM26</t>
+          <t>3674-603-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2457,27 +2457,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2491,13 +2491,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>34955.73</v>
+        <v>18540.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2598-232-CM26</t>
+          <t>5416-1043-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2522,27 +2522,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14843.82</v>
+        <v>215.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5416-1043-CM26</t>
+          <t>2598-232-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2583,27 +2583,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.495.960-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>215.27</v>
+        <v>14843.82</v>
       </c>
     </row>
     <row r="35">
@@ -2749,7 +2749,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3674-603-CM26</t>
+          <t>2859-1180-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2774,27 +2774,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>18540.2</v>
+        <v>5760.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>889473-1831-CM26</t>
+          <t>1237328-591-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2834,37 +2834,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4521.76</v>
+        <v>38735.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2598-237-CM26</t>
+          <t>859378-631-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
+          <t>76.086.318-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2934,13 +2934,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3620.46</v>
+        <v>31951.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4374-66-CM26</t>
+          <t>752-291-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2965,27 +2965,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2583.25</v>
+        <v>42869.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>859378-631-CM26</t>
+          <t>2598-237-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ATEM INTEGRACION TECNOLOGICA LIMITADA</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.086.318-1</t>
+          <t>77.495.960-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>31951.5</v>
+        <v>3620.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>752-291-CM26</t>
+          <t>889473-1831-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3082,48 +3082,52 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>42869.45</v>
+        <v>4521.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4374-65-CM26</t>
+          <t>4374-66-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3143,7 +3147,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3163,32 +3167,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7429.23</v>
+        <v>2583.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1237328-591-CM26</t>
+          <t>4374-65-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3208,32 +3208,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>38735.69</v>
+        <v>7429.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1220157-11-CM26</t>
+          <t>4374-64-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3278,17 +3278,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.511.000-2</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3312,13 +3312,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>15088.01</v>
+        <v>30176.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1305541-46-CM26</t>
+          <t>1220157-11-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3338,17 +3338,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.060-0</t>
+          <t>60.511.000-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1141.67</v>
+        <v>15088.01</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5952-168-CM26</t>
+          <t>1305541-46-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.981.060-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7476.18</v>
+        <v>1141.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>721703-490-CM26</t>
+          <t>5952-168-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3473,43 +3473,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3013.79</v>
+        <v>7476.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3413-84-CM26</t>
+          <t>721703-490-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3534,47 +3538,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.971.700-7</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3725.51</v>
+        <v>3013.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4374-64-CM26</t>
+          <t>3413-84-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3594,32 +3594,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>61.971.700-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>30176.02</v>
+        <v>3725.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5416-1066-CM26</t>
+          <t>4469-955-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3659,52 +3659,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>366.52</v>
+        <v>228.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2859-1222-CM26</t>
+          <t>3654-266-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3729,27 +3725,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3759,13 +3755,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2751.41</v>
+        <v>2341.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1562-470-CM26</t>
+          <t>2737-711-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3790,47 +3786,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7706.44</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1562-469-CM26</t>
+          <t>411-445-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3855,27 +3847,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3889,13 +3881,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1388.37</v>
+        <v>5289.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>411-445-CM26</t>
+          <t>1298355-852-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3915,52 +3907,48 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5289.55</v>
+        <v>5896.21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2737-711-CM26</t>
+          <t>1562-469-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3985,43 +3973,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>987.7</v>
+        <v>1388.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3654-266-CM26</t>
+          <t>1562-470-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4041,17 +4033,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4061,28 +4053,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2341.88</v>
+        <v>7706.44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4469-955-CM26</t>
+          <t>2859-1222-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4102,32 +4098,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4137,13 +4133,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>228.48</v>
+        <v>2751.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1298355-852-CM26</t>
+          <t>5416-1066-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4168,43 +4164,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5896.21</v>
+        <v>366.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1002588-254-CM26</t>
+          <t>1019-346-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4229,47 +4229,43 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>151320.4</v>
+        <v>19373.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1019-346-CM26</t>
+          <t>1002588-254-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4294,43 +4290,47 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>19373.32</v>
+        <v>151320.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1224957-803-CM26</t>
+          <t>3299-399-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4355,32 +4355,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7206.64</v>
+        <v>6302.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2294-2176-CM26</t>
+          <t>1224957-803-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4420,27 +4420,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4454,13 +4454,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2827.82</v>
+        <v>7206.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>697-307-CM26</t>
+          <t>1208910-263-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4485,27 +4485,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4457.54</v>
+        <v>1259.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-394-CM26</t>
+          <t>1208910-262-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4550,43 +4550,47 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.203.000-8</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4233.97</v>
+        <v>37485</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-395-CM26</t>
+          <t>3447-2829-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4606,32 +4610,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.203.000-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.495.960-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4641,13 +4645,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2760.13</v>
+        <v>1344.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3299-399-CM26</t>
+          <t>4498-157-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4667,37 +4671,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4706,13 +4710,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>6302.24</v>
+        <v>15848.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4498-157-CM26</t>
+          <t>2020-396-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4732,17 +4736,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>60.203.000-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4752,32 +4756,28 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>15848.8</v>
+        <v>1285.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3447-2829-CM26</t>
+          <t>2020-395-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4797,32 +4797,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>60.203.000-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4832,13 +4832,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1344.7</v>
+        <v>2760.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1208910-262-CM26</t>
+          <t>2020-394-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4863,47 +4863,43 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>60.203.000-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>37485</v>
+        <v>4233.97</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1208910-263-CM26</t>
+          <t>2294-2176-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4928,27 +4924,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4962,13 +4958,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1259.88</v>
+        <v>2827.82</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-396-CM26</t>
+          <t>697-307-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4993,37 +4989,41 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.203.000-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1285.15</v>
+        <v>4457.54</v>
       </c>
     </row>
     <row r="73">
@@ -5094,7 +5094,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1233616-1864-CM26</t>
+          <t>1233616-1863-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5134,32 +5134,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1632.68</v>
+        <v>20170.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1233616-1863-CM26</t>
+          <t>1233616-1862-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5199,28 +5195,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>20170.5</v>
+        <v>50249.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1233616-1862-CM26</t>
+          <t>1261-73-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5240,52 +5240,48 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>50249.54</v>
+        <v>2498.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1261-73-CM26</t>
+          <t>1609-362-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5310,27 +5306,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5340,13 +5336,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2498.99</v>
+        <v>10695.72</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1609-362-CM26</t>
+          <t>1233616-1864-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5366,42 +5362,46 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10695.72</v>
+        <v>1632.68</v>
       </c>
     </row>
     <row r="79">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5781,7 +5781,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>640840-190-CM26</t>
+          <t>2793-985-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5806,32 +5806,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5840,13 +5840,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10275.07</v>
+        <v>21241.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2793-985-CM26</t>
+          <t>1053139-170-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5871,47 +5871,43 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>21241.5</v>
+        <v>57596</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1053139-170-CM26</t>
+          <t>1019-350-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5936,37 +5932,41 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>57596</v>
+        <v>71997.98</v>
       </c>
     </row>
     <row r="88">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6220,7 +6220,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1237328-606-CM26</t>
+          <t>640840-190-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6245,43 +6245,47 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2826.73</v>
+        <v>10275.07</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1019-350-CM26</t>
+          <t>2013-1633-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6306,17 +6310,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6340,13 +6344,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>71997.98</v>
+        <v>34136.27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2013-1633-CM26</t>
+          <t>2013-1634-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6386,26 +6390,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>34136.27</v>
+        <v>4303.04</v>
       </c>
     </row>
     <row r="95">
@@ -6663,7 +6663,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2013-1634-CM26</t>
+          <t>697-309-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6688,43 +6688,47 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4303.04</v>
+        <v>1508.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>697-309-CM26</t>
+          <t>697-308-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6764,32 +6768,28 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1508.3</v>
+        <v>1499.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>697-308-CM26</t>
+          <t>1237328-606-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1499.4</v>
+        <v>2826.73</v>
       </c>
     </row>
     <row r="102">
@@ -6911,7 +6911,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1233623-942-CM26</t>
+          <t>1480972-761-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6936,43 +6936,47 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>31600.45</v>
+        <v>10504.13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1480972-761-CM26</t>
+          <t>1233623-942-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6997,41 +7001,37 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10504.13</v>
+        <v>31600.45</v>
       </c>
     </row>
     <row r="105">
@@ -7102,7 +7102,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5413-1112-CM26</t>
+          <t>1375757-698-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7122,48 +7122,52 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.495.960-2</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>982.7</v>
+        <v>6039.61</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1375757-698-CM26</t>
+          <t>5413-1112-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7183,52 +7187,48 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>6039.61</v>
+        <v>982.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>752-299-CM26</t>
+          <t>952751-351-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7253,37 +7253,41 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>27119.33</v>
+        <v>16200.18</v>
       </c>
     </row>
     <row r="109">
@@ -7541,7 +7545,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>952751-351-CM26</t>
+          <t>752-299-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7566,41 +7570,37 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16200.18</v>
+        <v>27119.33</v>
       </c>
     </row>
     <row r="114">
@@ -7980,7 +7980,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1233623-973-CM26</t>
+          <t>1428670-179-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8005,32 +8005,32 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.117.794-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>46731.3</v>
+        <v>5169.24</v>
       </c>
     </row>
     <row r="121">
@@ -8232,7 +8232,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1428670-179-CM26</t>
+          <t>1428670-181-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8272,26 +8272,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5169.24</v>
+        <v>1385.16</v>
       </c>
     </row>
     <row r="125">
@@ -8358,7 +8354,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1428670-181-CM26</t>
+          <t>1233623-973-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8383,37 +8379,41 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>65.117.794-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ASOCIACION METROPOLITANA DE MUNICIPALIDADES DE SANTIAGO SUR PARA LA GE</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1385.16</v>
+        <v>46731.3</v>
       </c>
     </row>
     <row r="127">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8870,7 +8870,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2765-535-CM26</t>
+          <t>3200-399-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8895,43 +8895,47 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>685.4299999999999</v>
+        <v>56870.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2765-534-CM26</t>
+          <t>2765-535-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8971,12 +8975,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8986,13 +8990,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1005.54</v>
+        <v>685.4299999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1191449-129-CM26</t>
+          <t>2765-534-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9017,12 +9021,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9047,13 +9051,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3016.61</v>
+        <v>1005.54</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1237328-652-CM26</t>
+          <t>1191449-129-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9078,17 +9082,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9108,13 +9112,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>32177.22</v>
+        <v>3016.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1238128-68-CM26</t>
+          <t>1237328-652-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9139,47 +9143,43 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>65.193.370-6</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE LA REINA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>903.21</v>
+        <v>32177.22</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2271-176-CM26</t>
+          <t>1457776-45-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9204,27 +9204,27 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9238,13 +9238,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>44382.24</v>
+        <v>20091.75</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2287-790-CM26</t>
+          <t>2271-176-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9303,13 +9303,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5291.34</v>
+        <v>44382.24</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2734-530-CM26</t>
+          <t>2287-790-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9368,13 +9368,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7363.72</v>
+        <v>5291.34</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3200-399-CM26</t>
+          <t>1238128-68-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9399,32 +9399,32 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>65.193.370-6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE LA REINA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9433,13 +9433,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>56870.1</v>
+        <v>903.21</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2287-803-CM26</t>
+          <t>2734-530-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9498,13 +9498,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>15767.5</v>
+        <v>7363.72</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1457776-45-CM26</t>
+          <t>2287-803-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9529,27 +9529,27 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>20091.75</v>
+        <v>15767.5</v>
       </c>
     </row>
     <row r="145">
@@ -9630,7 +9630,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>941739-99-CM26</t>
+          <t>1269832-35-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9655,27 +9655,27 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4788.54</v>
+        <v>8044.3</v>
       </c>
     </row>
     <row r="147">
@@ -9813,7 +9813,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1432083-2570-CM26</t>
+          <t>1227338-227-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9838,47 +9838,43 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>72.256.100-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>CORPORACION CULTURAL DE PENALOLEN</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2019.87</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1269832-35-CM26</t>
+          <t>1432083-2570-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9903,43 +9899,47 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>8044.3</v>
+        <v>2019.87</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1432083-2568-CM26</t>
+          <t>2429-1297-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9964,27 +9964,27 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4039.74</v>
+        <v>11369.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2429-1297-CM26</t>
+          <t>1110404-1023-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>11369.24</v>
+        <v>1206.66</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1110404-1023-CM26</t>
+          <t>941739-99-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10109,32 +10109,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1206.66</v>
+        <v>4788.54</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1227338-227-CM26</t>
+          <t>1432083-2568-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10159,37 +10155,41 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>72.256.100-7</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE PENALOLEN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>98.77</v>
+        <v>4039.74</v>
       </c>
     </row>
     <row r="155">
@@ -10260,7 +10260,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>558869-261-CM26</t>
+          <t>558869-260-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10300,28 +10300,32 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>67004.14</v>
+        <v>68889.53</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>558869-260-CM26</t>
+          <t>558869-259-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10361,12 +10365,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10380,13 +10384,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>68889.53</v>
+        <v>72653.07000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>558869-259-CM26</t>
+          <t>558869-261-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10426,26 +10430,22 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>72653.07000000001</v>
+        <v>67004.14</v>
       </c>
     </row>
     <row r="159">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10711,7 +10711,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1274285-373-CM26</t>
+          <t>5512-237-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10736,41 +10736,37 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>70.925.500-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5154.6</v>
+        <v>2927.4</v>
       </c>
     </row>
     <row r="164">
@@ -11024,7 +11020,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5512-237-CM26</t>
+          <t>1271356-134-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11049,27 +11045,27 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -11079,13 +11075,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2927.4</v>
+        <v>6854.28</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1271356-134-CM26</t>
+          <t>2448-1156-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11110,43 +11106,47 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>6854.28</v>
+        <v>8641.110000000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2448-1156-CM26</t>
+          <t>1274285-373-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11166,32 +11166,32 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.925.500-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8641.110000000001</v>
+        <v>5154.6</v>
       </c>
     </row>
     <row r="171">
@@ -11337,7 +11337,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>889473-2046-CM26</t>
+          <t>3363-108-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11362,47 +11362,43 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>192.66</v>
+        <v>15125.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3363-108-CM26</t>
+          <t>5517-438-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11427,12 +11423,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11442,12 +11438,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.139.769-9</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11457,7 +11453,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>15125.5</v>
+        <v>18183.2</v>
       </c>
     </row>
     <row r="175">
@@ -11483,7 +11479,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -11719,7 +11715,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1214102-2154-CM26</t>
+          <t>558869-263-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11744,47 +11740,43 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>273.51</v>
+        <v>66346.95</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>558869-262-CM26</t>
+          <t>889473-2046-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11809,27 +11801,27 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11843,7 +11835,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>72943.38</v>
+        <v>192.66</v>
       </c>
     </row>
     <row r="181">
@@ -12170,7 +12162,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>558869-263-CM26</t>
+          <t>1230848-223-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12195,12 +12187,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12210,28 +12202,32 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>66346.95</v>
+        <v>3091.16</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>558869-279-CM26</t>
+          <t>1230848-220-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12246,7 +12242,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12256,12 +12252,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12271,32 +12267,28 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>71702.56</v>
+        <v>25074.74</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5514-86-CM26</t>
+          <t>1214102-2154-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12311,7 +12303,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12321,43 +12313,47 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>37742.75</v>
+        <v>273.51</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>552975-661-CM26</t>
+          <t>558869-262-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12372,7 +12368,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12382,27 +12378,27 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -12416,13 +12412,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2283.35</v>
+        <v>72943.38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2429-1304-CM26</t>
+          <t>558869-279-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12447,12 +12443,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12481,13 +12477,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>33653.5</v>
+        <v>71702.56</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5517-437-CM26</t>
+          <t>5416-1151-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12512,47 +12508,43 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>8738.93</v>
+        <v>2903.6</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>979-1377-CM26</t>
+          <t>5514-86-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12577,27 +12569,27 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12607,13 +12599,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>63643.27</v>
+        <v>37742.75</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2429-1309-CM26</t>
+          <t>552975-661-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12638,27 +12630,27 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12672,13 +12664,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>30273.22</v>
+        <v>2283.35</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1036-281-CM26</t>
+          <t>2429-1309-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12693,7 +12685,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12703,43 +12695,47 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>804.39</v>
+        <v>30273.22</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5520-6511-CM26</t>
+          <t>2429-1304-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12754,7 +12750,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12764,27 +12760,27 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12798,13 +12794,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>6532.39</v>
+        <v>33653.5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1305504-211-CM26</t>
+          <t>5495-20-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12819,7 +12815,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12829,27 +12825,27 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12859,72 +12855,889 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3619.77</v>
+        <v>645.28</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>5490-138-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>3529.84</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>979-1377-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>63643.27</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>5517-437-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>8738.93</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1217466-128-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>60.905.003-9</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>2272.9</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1194619-57-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>2260.93</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>5520-6511-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>6532.39</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1305504-211-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>3619.77</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1070132-11-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.301.000-9</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>215.03</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1036-281-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>804.39</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
           <t>1238177-160-CM26</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2239-5-LR25</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
         <is>
           <t>65.165.009-7</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
         <is>
           <t>ECSA SPA</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
+      <c r="J206" t="inlineStr">
         <is>
           <t>77.976.242-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="K206" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M197" s="2" t="n">
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
         <v>29512</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1028871-664-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>14617.94</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2734-589-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.071.700-K</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>693.45</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>5060-887-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>892.49</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1110404-1041-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>1639.34</v>
       </c>
     </row>
   </sheetData>
